--- a/AAII_Financials/Yearly/IHG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IHG_YR_FIN.xlsx
@@ -2477,7 +2477,7 @@
         <v>263000</v>
       </c>
       <c r="F47" s="3">
-        <v>48000</v>
+        <v>233000</v>
       </c>
       <c r="G47" s="3">
         <v>192000</v>
@@ -2732,7 +2732,7 @@
         <v>328000</v>
       </c>
       <c r="F52" s="3">
-        <v>471000</v>
+        <v>286000</v>
       </c>
       <c r="G52" s="3">
         <v>228000</v>
@@ -4093,7 +4093,7 @@
         <v>55000</v>
       </c>
       <c r="E83" s="3">
-        <v>48000</v>
+        <v>50000</v>
       </c>
       <c r="F83" s="3">
         <v>150000</v>
